--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,29 +1099,29 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>20.51</v>
+        <v>-7.16</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,27 +1182,27 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,114 +1445,114 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>621.0381736526947</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>621.7871064467765</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>57.15</v>
+        <v>20.51</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,37 +1886,37 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>101.04</v>
+        <v>57.15</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>49.12</v>
+        <v>101.04</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>29.22</v>
+        <v>49.12</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,32 +3169,32 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
+          <t>-11.60699557296917</t>
         </is>
       </c>
       <c r="BC7" t="n">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,84 +3479,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,42 +3600,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-63.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.77</t>
+          <t>-66.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1444.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-27.80325964381511</t>
+          <t>-19.03028327210689</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>65.91</v>
+        <v>29.22</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,69 +3910,69 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.75</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-55.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>-61.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1444.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-44.84155867657123</t>
+          <t>-27.80325964381511</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-73.12</v>
+        <v>65.91</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-65.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,17 +4462,17 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -4482,17 +4482,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4502,32 +4502,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-50.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-51.02</t>
+          <t>-56.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,22 +4547,22 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-39.70032545890342</t>
+          <t>-44.84155867657123</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -4630,27 +4630,27 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-67.62</t>
+          <t>-65.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4893,126 +4893,126 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>20.51</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>20.67</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>20.19</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>20.04</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-47.24</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-51.02</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>621.0381736526947</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>20.67</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.17</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-43.77</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-45.23</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>621.7871064467765</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>158.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-106</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-33.62432256529601</t>
+          <t>-39.70032545890342</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-72.34999999999999</v>
+        <v>-73.12</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,109 +5188,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-67.62</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>-0.73</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-76.64</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,52 +5324,52 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-32.74</t>
+          <t>-43.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-39.24</t>
+          <t>-45.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>621.7871064467765</t>
+          <t>621.0381736526947</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>158.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -5434,16 +5434,16 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-192</t>
+          <t>-106</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-26.58305667198673</t>
+          <t>-33.62432256529601</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-70.92</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-16.65581857421808</t>
+          <t>-12.06591517969974</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-29.09891006586233</t>
+          <t>-15.35822892592142</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>8.660003881234232</t>
+          <t>6.139510302692406</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>618</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,32 +1029,32 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-7.16</v>
+        <v>-16.82</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,29 +1530,29 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>20.51</v>
+        <v>-7.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,39 +1740,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,119 +1871,119 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>620.5762331838565</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>621.0381736526947</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>57.15</v>
+        <v>20.51</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,37 +2317,37 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>101.04</v>
+        <v>57.15</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>49.12</v>
+        <v>101.04</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>29.22</v>
+        <v>49.12</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,84 +3489,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>-3.28</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>-0.49</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,37 +3595,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
+          <t>-11.60699557296917</t>
         </is>
       </c>
       <c r="BC8" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,84 +3910,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-3.28</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4026,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4076,27 +4076,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-63.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.77</t>
+          <t>-66.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1444.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-27.80325964381511</t>
+          <t>-19.03028327210689</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>65.91</v>
+        <v>29.22</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,69 +4341,69 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.54</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-55.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>-61.77</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1444.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-44.84155867657123</t>
+          <t>-27.80325964381511</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-73.12</v>
+        <v>65.91</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-65.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,22 +4888,22 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -4913,17 +4913,17 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4933,32 +4933,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-50.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.02</t>
+          <t>-56.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,22 +4978,22 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>621.0381736526947</t>
+          <t>620.5762331838565</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-39.70032545890342</t>
+          <t>-44.84155867657123</t>
         </is>
       </c>
       <c r="BC11" t="n">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-67.62</t>
+          <t>-65.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5319,131 +5319,131 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>10.34</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>20.51</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>20.67</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>20.19</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>20.04</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-47.24</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-51.02</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>620.5762331838565</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>20.67</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.17</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-43.77</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-45.23</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>621.0381736526947</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>158.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-106</t>
+          <t>-82</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-33.62432256529601</t>
+          <t>-39.70032545890342</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-72.34999999999999</v>
+        <v>-73.12</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>601</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-16.82</v>
+        <v>-37.27</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,32 +1460,32 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-7.16</v>
+        <v>-16.82</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,29 +1961,29 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>20.51</v>
+        <v>-7.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,119 +2302,119 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>619.694776119403</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>620.5762331838565</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>57.15</v>
+        <v>20.51</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,37 +2748,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>101.04</v>
+        <v>57.15</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>49.12</v>
+        <v>101.04</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>29.22</v>
+        <v>49.12</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4076,27 +4076,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
+          <t>-11.60699557296917</t>
         </is>
       </c>
       <c r="BC9" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,84 +4341,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.28</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3.54</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,47 +4457,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4507,27 +4507,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-63.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.77</t>
+          <t>-66.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1444.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-27.80325964381511</t>
+          <t>-19.03028327210689</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>65.91</v>
+        <v>29.22</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,69 +4772,69 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-3.54</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-55.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>-61.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1444.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-44.84155867657123</t>
+          <t>-27.80325964381511</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-73.12</v>
+        <v>65.91</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-65.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,22 +5319,22 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,32 +5364,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-50.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.02</t>
+          <t>-56.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>620.5762331838565</t>
+          <t>619.694776119403</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-39.70032545890342</t>
+          <t>-44.84155867657123</t>
         </is>
       </c>
       <c r="BC12" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,37 +1024,37 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-37.27</v>
+        <v>-51.69</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-16.82</v>
+        <v>-37.27</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,32 +1891,32 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-7.16</v>
+        <v>-16.82</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,29 +2392,29 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>20.51</v>
+        <v>-7.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,119 +2733,119 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>618.7846497764531</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>619.694776119403</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>57.15</v>
+        <v>20.51</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,37 +3179,37 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>101.04</v>
+        <v>57.15</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>49.12</v>
+        <v>101.04</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>29.22</v>
+        <v>49.12</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4507,27 +4507,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
+          <t>-11.60699557296917</t>
         </is>
       </c>
       <c r="BC10" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,84 +4772,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.54</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,47 +4888,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4938,27 +4938,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-63.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.77</t>
+          <t>-66.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1444.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-27.80325964381511</t>
+          <t>-19.03028327210689</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>65.91</v>
+        <v>29.22</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,69 +5203,69 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-50.22</t>
+          <t>-55.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-56.48</t>
+          <t>-61.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>619.694776119403</t>
+          <t>618.7846497764531</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1444.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-44.84155867657123</t>
+          <t>-27.80325964381511</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-73.12</v>
+        <v>65.91</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,37 +883,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,114 +1019,114 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.14</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-110.26</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-117.67</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>618.0848214285713</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-223.40</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-112.80</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>618.7846497764531</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1129,168 +1134,173 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-51.69</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-12.37364544544671</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-53.52671847265998</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>99</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-10.20</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1314,7 +1324,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,12 +1344,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1455,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,37 +1465,37 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,17 +1540,17 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1560,168 +1570,173 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-37.27</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4.891268531407928</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-51.69412238510046</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>6</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>-12.20</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,17 +1976,17 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1991,145 +2006,145 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-16.82</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>3.618341260172532</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-37.26562360340466</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>20</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>-12.20</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2144,15 +2159,20 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,12 +2327,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,32 +2342,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2362,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,17 +2412,17 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2422,168 +2442,173 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-7.16</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>11.05178941718657</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-16.82256735800337</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>208</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-9.76</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,29 +2848,29 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2853,168 +2878,173 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>16.11985428540292</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-7.160252458930074</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>81</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-9.53</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-9.76</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,114 +3199,114 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>618.0848214285713</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>618.7846497764531</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3284,168 +3314,173 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>20.35260096619074</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>20.50592069899363</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>101</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-11.31</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-9.53</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,37 +3645,37 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3650,22 +3685,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,12 +3720,12 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3715,168 +3750,173 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>101.04</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>20.32472465113567</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>57.15381375677771</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>161</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-10.42</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-11.31</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4156,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4146,168 +4186,173 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>13.62852663192802</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>101.0381676337272</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1197</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-6.65</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-10.42</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>21.05</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4592,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4577,168 +4622,173 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2.264135368399101</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>49.12159575673627</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>610</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-9.31</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-6.65</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,32 +4943,32 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,7 +4978,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4938,27 +4988,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5008,168 +5058,173 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-11.60699557296917</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>29.22108677228829</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>-9.31</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>20.45</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5193,7 +5248,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,84 +5258,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.99</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>54.20</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,42 +5379,42 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5369,27 +5424,27 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-55.39</t>
+          <t>-63.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.77</t>
+          <t>-66.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>618.7846497764531</t>
+          <t>618.0848214285713</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1444.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5439,168 +5494,173 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-27.80325964381511</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>65.91</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-19.03028327210689</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>29.22108677228829</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>61</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-9.09</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-9.31</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>21.54</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,32 +1034,32 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,22 +1104,22 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1129,21 +1129,21 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>99</v>
+        <v>321</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,114 +1455,114 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.14</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-110.26</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-117.67</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>617.8818722139673</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-223.40</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-112.80</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>618.0848214285713</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1570,16 +1570,16 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,37 +1901,37 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,22 +2139,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2778,207 +2778,207 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
+          <t>20.56</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>20.31</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-1828.49</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-98.66</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>617.8818722139673</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>349.6</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>11.05178941718657</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-16.82256735800337</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>208</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>20.64</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.31</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-228.65</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-92.51</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>618.0848214285713</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>16.11985428540292</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-7.160252458930074</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>81</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-9.76</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
       <c r="BW6" t="inlineStr">
         <is>
           <t>41.28%</t>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,29 +3284,29 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,114 +3635,114 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>617.8818722139673</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>618.0848214285713</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>57.15381375677771</t>
+          <t>20.50592069899363</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,37 +4081,37 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4121,22 +4121,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>101.0381676337272</t>
+          <t>57.15381375677771</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1197</v>
+        <v>161</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,19 +4319,19 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>49.12159575673627</t>
+          <t>101.0381676337272</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>610</v>
+        <v>1197</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>29.22108677228829</t>
+          <t>49.12159575673627</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,32 +5379,32 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5424,27 +5424,27 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.99</t>
+          <t>-71.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>618.0848214285713</t>
+          <t>617.8818722139673</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-19.03028327210689</t>
+          <t>-11.60699557296917</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>589</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,22 +5627,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,136 +1014,136 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-91.38</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-131.81</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>617.1810089020771</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>108.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>229.1</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>19.81</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-111.95</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-124.54</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>617.8818722139673</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>321.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>130.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>280.4</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>321</v>
+        <v>97</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,32 +1470,32 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,22 +1540,22 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1565,21 +1565,21 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>99</v>
+        <v>321</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,119 +1886,119 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.14</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-110.26</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-117.67</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>617.1810089020771</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-223.40</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-112.80</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>617.8818722139673</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA4" t="inlineStr">
         <is>
           <t>0</t>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,37 +2337,37 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,29 +3720,29 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,119 +4066,119 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>617.1810089020771</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>617.8818722139673</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>57.15381375677771</t>
+          <t>20.50592069899363</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,37 +4517,37 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4557,22 +4557,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>101.0381676337272</t>
+          <t>57.15381375677771</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1197</v>
+        <v>161</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,14 +4760,14 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>49.12159575673627</t>
+          <t>101.0381676337272</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>610</v>
+        <v>1197</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.96</t>
+          <t>-73.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>617.8818722139673</t>
+          <t>617.1810089020771</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11.60699557296917</t>
+          <t>-2.264135368399101</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>29.22108677228829</t>
+          <t>49.12159575673627</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,57 +1014,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1129,21 +1129,21 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,136 +1450,136 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-91.38</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-131.81</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>616.3111111111111</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>108.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>229.1</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>19.81</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-111.95</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-124.54</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>617.1810089020771</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>321.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>130.8</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>280.4</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>321</v>
+        <v>97</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,32 +1906,32 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,22 +1976,22 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -2001,21 +2001,21 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>99</v>
+        <v>321</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,119 +2322,119 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>20.33</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.14</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-110.26</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-117.67</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>616.3111111111111</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-223.40</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-112.80</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>617.1810089020771</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2442,16 +2442,16 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,37 +2773,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,22 +3011,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>349.6</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>349.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,29 +4156,29 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,119 +4502,119 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-163.68</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-88.23</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>616.3111111111111</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-2.10</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-136.49</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-83.41</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>617.1810089020771</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>57.15381375677771</t>
+          <t>20.50592069899363</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,37 +4953,37 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>101.0381676337272</t>
+          <t>57.15381375677771</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1197</v>
+        <v>161</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,19 +5191,19 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-68.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.95</t>
+          <t>-77.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>617.1810089020771</t>
+          <t>616.3111111111111</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2.264135368399101</t>
+          <t>13.62852663192802</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>49.12159575673627</t>
+          <t>101.0381676337272</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>610</v>
+        <v>1197</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-10.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>19.77</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>20.22</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>20.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>108.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>108.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>111.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-48.68691510600823</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>20</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>19.75</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>97.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>108.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>108.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>229.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-41.00708808746438</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>97</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>19.81</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>321.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>130.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>130.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>280.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-36.82136777213515</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>321</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>321.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>20.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>99.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>82.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>82.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-53.52671847265998</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>99</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>20.03</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-51.69412238510046</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>20.07</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>20.52</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>20.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>114.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>114.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-37.26562360340466</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>20</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>20.15</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>20.56</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.31</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.31</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>208.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>349.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>349.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-16.82256735800337</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>208</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>20.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.31</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>81.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>430</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-7.160252458930074</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>81</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>20.42</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>101.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>20.50592069899363</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>101</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>20.43</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>161.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>57.15381375677771</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>161</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>20.71</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1197.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>101.0381676337272</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1197</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1197.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1105,15 +1105,15 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,54 +1444,54 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1551,22 +1551,22 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN4" t="n">
         <v>20.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1965,15 +1965,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1981,22 +1981,22 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN5" t="n">
         <v>20.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2395,15 +2395,15 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,27 +2734,27 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2764,24 +2764,24 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2825,11 +2825,11 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,36 +3179,36 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN7" t="n">
         <v>20.32</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,11 +3255,11 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,11 +3685,11 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>349.6</v>
+        <v>114.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,31 +4044,31 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="AN9" t="n">
         <v>20.31</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>430</v>
+        <v>349.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.68</v>
+        <v>20.64</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.3</v>
+        <v>20.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4545,11 +4545,11 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>20.68</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-136.49</t>
+          <t>-163.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-83.41</t>
+          <t>-88.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>57.15381375677771</t>
+          <t>20.50592069899363</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>45.80</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.71</v>
+        <v>20.68</v>
       </c>
       <c r="AN12" t="n">
         <v>20.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-68.31</t>
+          <t>-136.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-83.41</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>13.62852663192802</t>
+          <t>20.32472465113567</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>101.0381676337272</t>
+          <t>57.15381375677771</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.42</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>597</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,14 +5566,14 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -908,12 +908,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-32.55766417198321</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-56.96438220958197</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,44 +1454,44 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,102 +1768,102 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-3.1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-52.60</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3.82</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,44 +1884,44 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1981,22 +1981,22 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN5" t="n">
         <v>20.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,20 +2390,20 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN6" t="n">
         <v>20.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,20 +2820,20 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,17 +3174,17 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3194,24 +3194,24 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,16 +3250,16 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3609,36 +3609,36 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN8" t="n">
         <v>20.32</v>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,16 +3680,16 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,16 +4110,16 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>349.6</v>
+        <v>114.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,31 +4474,31 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="AN10" t="n">
         <v>20.31</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,16 +4540,16 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>430</v>
+        <v>349.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.68</v>
+        <v>20.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.3</v>
+        <v>20.31</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,16 +4970,16 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,44 +5324,44 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>20.68</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-136.49</t>
+          <t>-163.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.41</t>
+          <t>-88.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>616.3111111111111</t>
+          <t>615.4038461538462</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.32472465113567</t>
+          <t>20.35260096619074</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>57.15381375677771</t>
+          <t>20.50592069899363</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,37 +883,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,49 +1019,49 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-32.55766417198321</t>
+          <t>-33.94537627650134</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-56.96438220958197</t>
+          <t>-41.57779285135109</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-32.55766417198321</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-56.96438220958197</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,20 +1960,20 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,49 +2309,49 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN6" t="n">
         <v>20.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,20 +2820,20 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN7" t="n">
         <v>20.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,20 +3250,20 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,22 +3599,22 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3624,24 +3624,24 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,16 +3680,16 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,36 +4039,36 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN9" t="n">
         <v>20.32</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,16 +4110,16 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,16 +4540,16 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>349.6</v>
+        <v>114.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,31 +4904,31 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="AN11" t="n">
         <v>20.31</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,16 +4970,16 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>430</v>
+        <v>349.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.68</v>
+        <v>20.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.3</v>
+        <v>20.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-163.68</t>
+          <t>-228.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-92.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,16 +5400,16 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>615.4038461538462</t>
+          <t>615.0044313146234</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.35260096619074</t>
+          <t>16.11985428540292</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>20.50592069899363</t>
+          <t>-7.160252458930074</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1029,39 +1029,39 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-33.94537627650134</t>
+          <t>-35.93343153847124</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-41.57779285135109</t>
+          <t>-46.86773547930569</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,37 +1313,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1454,44 +1454,44 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-32.55766417198321</t>
+          <t>-33.94537627650134</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-56.96438220958197</t>
+          <t>-41.57779285135109</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,22 +1950,22 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-32.55766417198321</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-56.96438220958197</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2314,44 +2314,44 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,30 +2380,30 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN7" t="n">
         <v>20.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,30 +3240,30 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN8" t="n">
         <v>20.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,30 +3670,30 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4034,17 +4034,17 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4054,24 +4054,24 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,26 +4100,26 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4469,36 +4469,36 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN10" t="n">
         <v>20.32</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,26 +4530,26 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,26 +4960,26 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>349.6</v>
+        <v>114.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,31 +5334,31 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="AN12" t="n">
         <v>20.31</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-228.65</t>
+          <t>-1828.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,26 +5390,26 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-98.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>615.0044313146234</t>
+          <t>614.1017699115044</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>430</v>
+        <v>349.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16.11985428540292</t>
+          <t>11.05178941718657</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7.160252458930074</t>
+          <t>-16.82256735800337</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -908,14 +908,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>0</t>
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,60 +1029,60 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35.93343153847124</t>
+          <t>-37.61563214475346</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,14 +1338,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,39 +1459,39 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-33.94537627650134</t>
+          <t>-35.93343153847124</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-41.57779285135109</t>
+          <t>-46.86773547930569</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,39 +1743,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-32.55766417198321</t>
+          <t>-33.94537627650134</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-56.96438220958197</t>
+          <t>-41.57779285135109</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-32.55766417198321</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-56.96438220958197</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2825,15 +2825,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN8" t="n">
         <v>20.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,15 +3685,15 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN9" t="n">
         <v>20.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,15 +4115,15 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,39 +4323,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,27 +4454,27 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4484,24 +4484,24 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4545,11 +4545,11 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,36 +4899,36 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN11" t="n">
         <v>20.32</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4975,11 +4975,11 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.31</v>
+        <v>20.32</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1828.49</t>
+          <t>-495.17</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.66</t>
+          <t>-105.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5405,11 +5405,11 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>349.6</v>
+        <v>114.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>11.05178941718657</t>
+          <t>3.618341260172532</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-16.82256735800337</t>
+          <t>-37.26562360340466</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>354.12</t>
+          <t>360.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>603</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1024,44 +1024,44 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-37.61563214475346</t>
+          <t>-39.0390326577615</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1459,60 +1459,60 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-35.93343153847124</t>
+          <t>-37.61563214475346</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1889,39 +1889,39 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-33.94537627650134</t>
+          <t>-35.93343153847124</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-41.57779285135109</t>
+          <t>-46.86773547930569</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,39 +2173,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2314,44 +2314,44 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-32.55766417198321</t>
+          <t>-33.94537627650134</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-56.96438220958197</t>
+          <t>-41.57779285135109</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-32.55766417198321</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-56.96438220958197</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,44 +3174,44 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3255,15 +3255,15 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.12007907423797</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3604,44 +3604,44 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-24.38065434118883</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.68691510600823</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN9" t="n">
         <v>20.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4115,15 +4115,15 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-19.96133420213076</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-41.00708808746438</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN10" t="n">
         <v>20.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4545,15 +4545,15 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -4561,22 +4561,22 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-16.13483349570647</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.82136777213515</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,39 +4753,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -4914,24 +4914,24 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-223.40</t>
+          <t>-110.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4975,11 +4975,11 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-12.37364544544671</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.52671847265998</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5329,36 +5329,36 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.52</v>
+        <v>20.42</v>
       </c>
       <c r="AN12" t="n">
         <v>20.32</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-495.17</t>
+          <t>-223.40</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-112.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5405,11 +5405,11 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>114.2</v>
+        <v>83.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3.618341260172532</t>
+          <t>-4.891268531407928</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-37.26562360340466</t>
+          <t>-51.69412238510046</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>360.23</t>
+          <t>358.35</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>8923</t>
@@ -883,34 +879,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -918,7 +914,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +924,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,37 +1015,33 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.31</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
+          <t>83.07</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,30 +1050,26 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>17.98</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>15.43</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.14</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>338.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39.0390326577615</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-46.86773547930569</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1199,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1214,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1229,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1254,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>8923</t>
@@ -1338,7 +1322,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1332,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1342,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1423,7 +1407,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1449,49 +1433,45 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.47</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
+          <t>84.31</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.24</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,18 +1480,14 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.03</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>17.98</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,7 +1506,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1539,34 +1515,34 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>338.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-37.61563214475346</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-46.86773547930569</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1607,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1622,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1647,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>8923</t>
@@ -1768,7 +1740,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1750,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1760,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,7 +1825,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1879,7 +1851,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,59 +1861,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.59</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
+          <t>76.47</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.5</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
+          <t>12.03</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>89.25</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>338.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-35.93343153847124</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46.86773547930569</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2025,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2040,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2050,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2065,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2161,11 +2125,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>8923</t>
@@ -2173,12 +2133,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,7 +2158,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2168,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2178,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2283,17 +2243,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2269,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,39 +2279,35 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.64</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
+          <t>70.59</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,18 +2316,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.83</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.16</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2332,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2342,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>338.51</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-33.94537627650134</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-41.57779285135109</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2443,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2458,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2468,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2483,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2508,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,42 +2555,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2600,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2655,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2665,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,49 +2691,45 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>53.82</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
+          <t>62.64</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.44</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,18 +2738,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.55</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
+          <t>-6.83</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.16</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2754,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2764,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>339.25</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-32.55766417198321</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-56.96438220958197</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2820,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2865,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2875,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2890,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2905,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2930,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3058,7 +3002,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3012,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3022,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,7 +3087,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,69 +3113,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.54</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
+          <t>53.82</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.47</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>-22.55</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.16</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3176,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3186,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>114.85</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98.825</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>336.47</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-28.12007907423797</t>
+          <t>-31.86549629802587</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-49.37788809803976</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3356,7 +3292,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3302,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3312,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3327,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3463,12 +3399,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,7 +3424,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3434,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3444,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3573,17 +3509,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,49 +3535,45 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-2.23</t>
-        </is>
+          <t>37.54</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.97</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,18 +3582,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.24</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
+          <t>-36.47</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3598,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3608,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>108.6</v>
+        <v>134.25</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>108.725</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>337.05</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-24.38065434118883</t>
+          <t>-28.68142506165971</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-48.68691510600823</t>
+          <t>-43.67241057329801</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>134.25</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3709,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3724,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3734,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3749,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3774,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3821,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3836,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3846,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3866,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3921,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3931,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,49 +3957,45 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.33</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2.23</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,18 +4004,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-91.38</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
+          <t>-57.24</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.14</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4020,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,12 +4030,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
@@ -4123,30 +4043,30 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>336.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-19.96133420213076</t>
+          <t>-25.95579133227093</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-41.00708808746438</t>
+          <t>-48.13164230319202</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4086,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4131,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4156,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4171,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4196,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4233,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4243,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4258,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4268,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4278,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4288,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4343,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4353,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,69 +4379,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-2.48</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN10" t="n">
         <v>20.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-111.95</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>-91.38</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.12</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4442,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4452,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>337.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16.13483349570647</t>
+          <t>-21.92381842846709</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-36.82136777213515</t>
+          <t>-40.54191469221232</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4508,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4553,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4578,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4593,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4618,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4633,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4665,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4680,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4690,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4700,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4710,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4765,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4775,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,12 +4801,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4902,56 +4814,48 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
+      <c r="AH11" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-2.58</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN11" t="n">
         <v>20.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-110.26</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
+          <t>-111.95</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4864,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4874,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>338.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12.37364544544671</t>
+          <t>-18.53871001687705</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-53.52671847265998</t>
+          <t>-36.50152115180518</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4930,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4975,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +4985,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5000,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5015,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5040,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,42 +5087,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-72.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5132,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5187,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5197,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,49 +5223,45 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.91</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,18 +5270,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-223.40</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
+          <t>-110.26</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5286,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.80</t>
+          <t>-117.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5296,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>614.1017699115044</t>
+          <t>613.3276877761414</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>337.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-216</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4.891268531407928</t>
+          <t>-15.27274435598103</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-51.69412238510046</t>
+          <t>-53.42590462437335</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5352,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5397,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5407,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5422,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5437,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5462,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>8923</t>
@@ -879,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -894,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -909,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1010,50 +1014,50 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1062,11 +1066,11 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.14</v>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1199,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1254,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1264,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>8923</t>
@@ -1297,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1322,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1428,38 +1436,38 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1468,26 +1476,26 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AQ3" t="n">
         <v>-0.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,20 +1514,20 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="AZ3" t="n">
@@ -1527,22 +1535,22 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1607,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1617,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1632,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>8923</t>
@@ -1740,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1825,7 +1837,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1846,50 +1858,50 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1898,11 +1910,11 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.15</v>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,7 +1936,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1933,11 +1945,11 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1945,17 +1957,17 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -2025,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2040,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2050,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2125,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>8923</t>
@@ -2158,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2243,7 +2259,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2264,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2279,52 +2295,52 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ5" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR5" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AR5" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -2332,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2342,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2443,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2458,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2468,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2483,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2545,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2555,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2580,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2665,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2686,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2701,35 +2717,35 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2738,11 +2754,11 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.16</v>
@@ -2754,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2764,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2865,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2880,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2905,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2930,17 +2946,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2977,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2992,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3002,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3077,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3087,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3108,50 +3124,50 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.17</v>
+        <v>-1.44</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3160,11 +3176,11 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.16</v>
@@ -3176,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3186,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>114.85</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98.825</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>336.47</v>
+        <v>339.25</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-31.86549629802587</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-49.37788809803976</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3242,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3287,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3297,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3312,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3327,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3352,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3424,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3525,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3530,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3598,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3608,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>134.25</v>
+        <v>114.85</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>108.725</t>
+          <t>98.825</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>337.05</v>
+        <v>336.47</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-28.68142506165971</t>
+          <t>-31.86549629802587</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-43.67241057329801</t>
+          <t>-49.37788809803976</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>134.25</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3714,7 +3730,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3724,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3734,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3749,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3821,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3846,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3931,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3952,50 +3968,50 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.23</v>
+        <v>-1.97</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4004,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4020,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4030,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>108.6</v>
+        <v>134.25</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>108.725</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>336.36</v>
+        <v>337.05</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-25.95579133227093</t>
+          <t>-28.68142506165971</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-48.13164230319202</t>
+          <t>-43.67241057329801</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>134.25</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4131,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4146,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4156,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4171,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4196,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4243,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4258,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4268,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4343,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4353,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4374,50 +4390,50 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-1.27</v>
+        <v>0.66</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4426,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4442,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4452,12 +4468,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
@@ -4465,30 +4481,30 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>337.52</v>
+        <v>336.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-21.92381842846709</t>
+          <t>-25.95579133227093</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-40.54191469221232</t>
+          <t>-48.13164230319202</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4508,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4553,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4563,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4578,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4593,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4618,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4655,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4665,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4680,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4690,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4765,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4775,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4796,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-2.07</v>
+        <v>-1.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.58</v>
+        <v>-2.48</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN11" t="n">
         <v>20.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4864,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4874,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>338.68</v>
+        <v>337.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-18.53871001687705</t>
+          <t>-21.92381842846709</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-36.50152115180518</t>
+          <t>-40.54191469221232</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4930,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4985,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5000,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5015,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5040,12 +5056,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5055,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5087,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5102,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5112,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-72.33</t>
+          <t>-53.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5187,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5197,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5218,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5237,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>-2.07</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.91</v>
+        <v>-2.58</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="AN12" t="n">
         <v>20.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-110.26</t>
+          <t>-111.95</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5286,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.67</t>
+          <t>-124.54</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5296,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>613.3276877761414</t>
+          <t>612.5183823529412</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>82.8</v>
+        <v>130.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>299.2</t>
+          <t>280.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>337.32</v>
+        <v>338.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-216</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-15.27274435598103</t>
+          <t>-18.53871001687705</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-53.42590462437335</t>
+          <t>-36.50152115180518</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5352,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5397,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5407,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5422,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5437,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>598</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5462,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1024,40 +1024,40 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.14</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,102 +1330,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-30.21</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-4.14</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-12.46</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>3.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1446,40 +1446,40 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1488,11 +1488,11 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.14</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,42 +1727,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1868,28 +1868,28 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1898,26 +1898,26 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>-0.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,20 +1936,20 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -1957,22 +1957,22 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2290,40 +2290,40 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2332,11 +2332,11 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.15</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2367,11 +2367,11 @@
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2717,52 +2717,52 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ6" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR6" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AR6" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,11 +3176,11 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.16</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3556,40 +3556,40 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.17</v>
+        <v>-1.44</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,11 +3598,11 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.16</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>114.85</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>98.825</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>336.47</v>
+        <v>339.25</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-31.86549629802587</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-49.37788809803976</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3978,56 +3978,56 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>134.25</v>
+        <v>114.85</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>108.725</t>
+          <t>98.825</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>337.05</v>
+        <v>336.47</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-28.68142506165971</t>
+          <t>-31.86549629802587</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-43.67241057329801</t>
+          <t>-49.37788809803976</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>134.25</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4400,40 +4400,40 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.23</v>
+        <v>-1.97</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>108.6</v>
+        <v>134.25</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>108.725</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>336.36</v>
+        <v>337.05</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-25.95579133227093</t>
+          <t>-28.68142506165971</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-48.13164230319202</t>
+          <t>-43.67241057329801</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>134.25</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4822,40 +4822,40 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.27</v>
+        <v>0.66</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
@@ -4903,30 +4903,30 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>337.52</v>
+        <v>336.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-21.92381842846709</t>
+          <t>-25.95579133227093</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-40.54191469221232</t>
+          <t>-48.13164230319202</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-52.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5244,56 +5244,56 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.07</v>
+        <v>-1.27</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.58</v>
+        <v>-2.48</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="AN12" t="n">
         <v>20.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-111.95</t>
+          <t>-91.38</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.54</t>
+          <t>-131.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>612.5183823529412</t>
+          <t>611.762114537445</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>130.8</v>
+        <v>108.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>229.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>338.68</v>
+        <v>337.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-18.53871001687705</t>
+          <t>-21.92381842846709</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-36.50152115180518</t>
+          <t>-40.54191469221232</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1024,191 +1024,191 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>610.9618768328446</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>611.762114537445</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1446,40 +1446,40 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1488,11 +1488,11 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.14</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,102 +1752,102 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-30.21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-4.14</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-12.46</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>3.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1868,40 +1868,40 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.14</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,42 +2149,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2290,28 +2290,28 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2320,26 +2320,26 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>-0.12</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,20 +2358,20 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2379,22 +2379,22 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2712,40 +2712,40 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2754,11 +2754,11 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.15</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2789,11 +2789,11 @@
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3139,52 +3139,52 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR7" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AR7" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3561,35 +3561,35 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,11 +3598,11 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.16</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,42 +3837,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3978,40 +3978,40 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.17</v>
+        <v>-1.44</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.16</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>114.85</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>98.825</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>336.47</v>
+        <v>339.25</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-31.86549629802587</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-49.37788809803976</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4400,56 +4400,56 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>134.25</v>
+        <v>114.85</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>108.725</t>
+          <t>98.825</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>337.05</v>
+        <v>336.47</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-28.68142506165971</t>
+          <t>-31.86549629802587</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-43.67241057329801</t>
+          <t>-49.37788809803976</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>134.25</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4681,34 +4681,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4822,40 +4822,40 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.23</v>
+        <v>-1.97</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>108.6</v>
+        <v>134.25</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>108.725</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>336.36</v>
+        <v>337.05</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-25.95579133227093</t>
+          <t>-28.68142506165971</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-48.13164230319202</t>
+          <t>-43.67241057329801</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>134.25</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-52.60</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5244,40 +5244,40 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.27</v>
+        <v>0.66</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.33</v>
+        <v>20.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-57.24</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-131.81</t>
+          <t>-137.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>611.762114537445</t>
+          <t>610.9618768328446</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
@@ -5325,30 +5325,30 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>229.1</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>337.52</v>
+        <v>336.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-21.92381842846709</t>
+          <t>-25.95579133227093</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-40.54191469221232</t>
+          <t>-48.13164230319202</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,35 +1029,35 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.13</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,193 +1441,193 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>610.0717423133236</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>610.9618768328446</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
           <t>4.23</t>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,45 +1863,45 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.14</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,45 +2285,45 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2332,11 +2332,11 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.14</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,33 +2707,33 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2742,26 +2742,26 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>-0.12</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,20 +2780,20 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -2801,22 +2801,22 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3129,45 +3129,45 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,11 +3176,11 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.15</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3211,11 +3211,11 @@
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="AZ7" t="n">
@@ -3223,17 +3223,17 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,52 +3561,52 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AQ8" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR8" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AR8" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,35 +3983,35 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.16</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,45 +4395,45 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.17</v>
+        <v>-1.44</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4442,11 +4442,11 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.16</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>114.85</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>98.825</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>336.47</v>
+        <v>339.25</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-31.86549629802587</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-49.37788809803976</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>20.19</v>
+        <v>20.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.35</v>
+        <v>20.36</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-22.55</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-140.84</t>
+          <t>-143.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>134.25</v>
+        <v>114.85</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>108.725</t>
+          <t>98.825</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>337.05</v>
+        <v>336.47</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-28.68142506165971</t>
+          <t>-31.86549629802587</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-43.67241057329801</t>
+          <t>-49.37788809803976</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>134.25</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5103,34 +5103,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,45 +5239,45 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.23</v>
+        <v>-1.97</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.77</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.22</v>
+        <v>20.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-57.24</t>
+          <t>-36.47</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.12</t>
+          <t>-140.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>610.9618768328446</t>
+          <t>610.0717423133236</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>108.6</v>
+        <v>134.25</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>108.725</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>336.36</v>
+        <v>337.05</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-25.95579133227093</t>
+          <t>-28.68142506165971</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-48.13164230319202</t>
+          <t>-43.67241057329801</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>134.25</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -913,7 +913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1109,35 +1109,35 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="AV2" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1146,11 +1146,11 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0.12</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1177,38 +1177,38 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
@@ -1385,42 +1385,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,50 +1556,50 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1608,14 +1608,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1639,38 +1639,38 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2033,35 +2033,35 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2070,11 +2070,11 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0.13</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2101,38 +2101,38 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,201 +2480,201 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>609.2280701754386</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>609.2280701754386</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BH5" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2729,17 +2729,17 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,50 +2942,50 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AV6" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -2994,11 +2994,11 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0.14</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3025,38 +3025,38 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,50 +3404,50 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AV7" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -3456,11 +3456,11 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0.14</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3487,38 +3487,38 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,42 +3695,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,38 +3866,38 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -3906,26 +3906,26 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AV8" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AY8" t="n">
         <v>-0.12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3949,15 +3949,15 @@
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="BH8" t="n">
@@ -3965,22 +3965,22 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -4328,50 +4328,50 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AV9" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -4380,11 +4380,11 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0.15</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4415,11 +4415,11 @@
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="BH9" t="n">
@@ -4427,17 +4427,17 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -4790,12 +4790,12 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4805,52 +4805,52 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AV10" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AY10" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="BA10" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4873,38 +4873,38 @@
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,12 +5252,12 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5267,35 +5267,35 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AV11" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5304,11 +5304,11 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AZ11" t="n">
         <v>-0.16</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5335,38 +5335,38 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,17 +5496,17 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
@@ -5543,42 +5543,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5693,17 +5693,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,50 +5714,50 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.17</v>
+        <v>-1.44</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>20.16</v>
+        <v>20.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>20.36</v>
+        <v>20.37</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-22.55</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0.16</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-143.28</t>
+          <t>-144.03</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5797,38 +5797,38 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>114.85</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>98.825</t>
+          <t>113.725</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>336.47</v>
+        <v>339.25</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-31.86549629802587</t>
+          <t>-32.35346227723851</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-49.37788809803976</t>
+          <t>-35.03727516290797</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>611</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-1.21</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-2.17</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>19.84</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>19.86</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>20.3</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-4.74</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-134.12</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="n">
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
         <v>33.25</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>42.525</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>237.06</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-32.04429981332186</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-27.87588519809319</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>33.25</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-13.08</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-1.31</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-2.27</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>19.86</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>19.9</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>20.36</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>7.55</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-133.71</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>35</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>62.2</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>271.17</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-32.80219337972708</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-30.34365594848241</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-13.08</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>76.19</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-2.17</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>19.92</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>19.94</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>20.38</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>27.54</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-134.35</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>42.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>60.2</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>284.98</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-33.24920018540792</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-31.5799835937355</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-10.86</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>20.1</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>42.86</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-2.24</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>19.91</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>19.93</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>20.39</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>16.99</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-136.71</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>57.6</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>73.425</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>285.38</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-33.55269411116655</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-30.0754522443208</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-10.86</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>20.1</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>20.1</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>33.77</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-2.27</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>19.94</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>20.4</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>2.88</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-138.27</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>71.025</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>293.08</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-34.1849199051385</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-31.35199845071691</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-12.20</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-1.02</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>57.58</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.26</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-2.03</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>20</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>20.42</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-138.55</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>42.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>51.8</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>74.225</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>315.32</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-34.69999653321515</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-34.30592165804288</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>42.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-12.64</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>3.65</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>72.73</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>83.07</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-1.92</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>20.02</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>20.04</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>20.43</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>15.43</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-138.99</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>102.125</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>338.94</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-34.7716465105192</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-34.83631475214987</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-11.75</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>84.31</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.15</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-1.71</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>20.02</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>20.07</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>20.42</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>20.12</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>17.98</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.15</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-140.49</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
         <v>78</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>106.125</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>338.94</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-28</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-34.75988864840453</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-36.17129364544024</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-11.09</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>76.47</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>76.47</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>0.3</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-1.51</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>19.99</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>20.09</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>20.4</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>20.12</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>12.03</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.15</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-142.31</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
         <v>89.25</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>98.925</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>338.94</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-34.5032695580344</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-38.8222887199465</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-11.09</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
         <is>
           <t>76.47</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>70.59</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.45</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-1.32</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>19.96</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>20.11</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>20.38</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>4.09</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-143.59</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>93.125</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>338.51</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-33.71799334677766</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-41.22291422924303</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-11.09</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>19.5</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/08/27</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>9.16</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
         <is>
           <t>76.47</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>62.64</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>1.01</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-1.44</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-1.13</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>20.14</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>20.37</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-6.83</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-144.03</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>609.2280701754386</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>230.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>96.65000000000001</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>113.725</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>339.25</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-32.35346227723851</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-35.03727516290797</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>230.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/10/01</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-11.09</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>時報</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-12.06591517969974</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-15.35822892592142</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>6.139510302692406</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>41.28%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-6.63%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>叢書類78.96%、外版及其他21.00%、漫畫書0.04% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>時報-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>14.69</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 文化創意業 - 出版產業</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1149,35 +1149,35 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.21</v>
+        <v>-1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>19.86</v>
+        <v>19.85</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1186,15 +1186,15 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BC2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BD2" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BD2" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BE2" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>33.25</v>
+        <v>24.78</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>237.06</v>
+        <v>210.11</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1631,35 +1631,35 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BD3" t="n">
         <v>-0.12</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1699,38 +1699,38 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1907,42 +1907,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,7 +2098,7 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -2108,40 +2108,40 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2181,38 +2181,38 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,7 +2580,7 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2595,35 +2595,35 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2632,11 +2632,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="BD5" t="n">
         <v>-0.13</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2663,38 +2663,38 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,7 +3062,7 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -3072,188 +3072,188 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/12/02</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>609.2280701754386</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BL6" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>609.2280701754386</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
           <t>4.23</t>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,7 +3544,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3554,40 +3554,40 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BD7" t="n">
         <v>-0.14</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3627,38 +3627,38 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,7 +4026,7 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -4036,40 +4036,40 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -4078,11 +4078,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.14</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4109,38 +4109,38 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,42 +4317,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,7 +4508,7 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4518,28 +4518,28 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4548,26 +4548,26 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="BC9" t="n">
         <v>-0.12</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4591,15 +4591,15 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4990,7 +4990,7 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -5000,40 +5000,40 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -5042,11 +5042,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.15</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5077,11 +5077,11 @@
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -5089,17 +5089,17 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5472,7 +5472,7 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5487,52 +5487,52 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="BC11" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BD11" t="n">
         <v>-0.15</v>
       </c>
-      <c r="BD11" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="BE11" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5555,38 +5555,38 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,7 +5954,7 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5969,35 +5969,35 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="BD12" t="n">
         <v>-0.16</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-144.03</t>
+          <t>-143.59</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6037,38 +6037,38 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>96.65000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>113.725</t>
+          <t>93.125</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>339.25</v>
+        <v>338.51</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-32.35346227723851</t>
+          <t>-33.71799334677766</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-35.03727516290797</t>
+          <t>-41.22291422924303</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,187 +943,187 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-16.86</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-44.42</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,61 +1139,61 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.01</v>
+        <v>3.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>19.85</v>
+        <v>19.89</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,53 +1202,53 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-135.07</t>
+          <t>-132.31</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>24.78</v>
+        <v>40.98</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>44.59166666666667</t>
+          <t>49.29166666666667</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>210.11</v>
+        <v>208.03</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-31.15214577171364</t>
+          <t>-28.93993187154836</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-26.2452985428684</t>
+          <t>-16.77275542063935</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>22.66666666666667</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1373,27 +1373,27 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,35 +1631,35 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.21</v>
+        <v>-1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>19.86</v>
+        <v>19.85</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1668,15 +1668,15 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BC3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BD3" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BD3" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BE3" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>33.25</v>
+        <v>24.78</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>237.06</v>
+        <v>210.11</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BD4" t="n">
         <v>-0.12</v>
@@ -2166,53 +2166,53 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2337,22 +2337,22 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,45 +2585,45 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,53 +2648,53 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2819,27 +2819,27 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,35 +3077,35 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3114,11 +3114,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="BD6" t="n">
         <v>-0.13</v>
@@ -3130,53 +3130,53 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3301,22 +3301,22 @@
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,196 +3549,196 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>608.6124087591242</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BL7" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>609.2280701754386</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,45 +4031,45 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -4078,11 +4078,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.14</v>
@@ -4094,53 +4094,53 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4265,27 +4265,27 @@
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,45 +4513,45 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.14</v>
@@ -4576,53 +4576,53 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,33 +4995,33 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -5030,26 +5030,26 @@
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="BC10" t="n">
         <v>-0.12</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,30 +5058,30 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -5089,22 +5089,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5229,27 +5229,27 @@
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5477,45 +5477,45 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5524,11 +5524,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BD11" t="n">
         <v>-0.15</v>
@@ -5540,17 +5540,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5559,11 +5559,11 @@
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="BL11" t="n">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-9.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,52 +5969,52 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.77</v>
+        <v>-0.5</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>20.11</v>
+        <v>20.09</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="BC12" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-0.15</v>
       </c>
-      <c r="BD12" t="n">
-        <v>-0.16</v>
-      </c>
       <c r="BE12" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -6022,53 +6022,53 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-143.59</t>
+          <t>-142.31</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>609.2280701754386</t>
+          <t>608.6124087591242</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>77.65000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>93.125</t>
+          <t>98.925</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>338.51</v>
+        <v>338.94</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-33.71799334677766</t>
+          <t>-34.5032695580344</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-41.22291422924303</t>
+          <t>-38.8222887199465</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.04</v>
+        <v>0.19</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>19.89</v>
+        <v>19.92</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20.29</v>
+        <v>20.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>73.72</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-132.31</t>
+          <t>-127.28</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>40.98</v>
+        <v>40.78</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>49.29166666666667</t>
+          <t>41.59166666666667</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>208.03</v>
+        <v>207.31</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-28.93993187154836</t>
+          <t>-27.41419717585831</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-16.77275542063935</t>
+          <t>-19.02265634956301</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-16.86</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-44.42</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.01</v>
+        <v>3.12</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>19.85</v>
+        <v>19.89</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-135.07</t>
+          <t>-132.31</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>24.78</v>
+        <v>40.98</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>44.59166666666667</t>
+          <t>49.29166666666667</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>210.11</v>
+        <v>208.03</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-31.15214577171364</t>
+          <t>-28.93993187154836</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-26.2452985428684</t>
+          <t>-16.77275542063935</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>22.66666666666667</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.21</v>
+        <v>-1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>19.86</v>
+        <v>19.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,15 +2150,15 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BC4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BD4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BD4" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BE4" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>33.25</v>
+        <v>24.78</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>237.06</v>
+        <v>210.11</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,35 +2595,35 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2632,11 +2632,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BD5" t="n">
         <v>-0.12</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,45 +3067,45 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,35 +3559,35 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="BD7" t="n">
         <v>-0.13</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,196 +4031,196 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>607.7274052478134</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>608.6124087591242</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,45 +4513,45 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.14</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,45 +4995,45 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -5042,11 +5042,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.14</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.50</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,33 +5477,33 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5512,26 +5512,26 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>20.07</v>
+        <v>20.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="BC11" t="n">
         <v>-0.12</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-140.49</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,20 +5550,20 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>78</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>106.125</t>
+          <t>102.125</t>
         </is>
       </c>
       <c r="BL11" t="n">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-34.75988864840453</t>
+          <t>-34.7716465105192</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-36.17129364544024</t>
+          <t>-34.83631475214987</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.78</t>
+          <t>-26.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5959,45 +5959,45 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.4</v>
+        <v>20.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -6006,11 +6006,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BD12" t="n">
         <v>-0.15</v>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-142.31</t>
+          <t>-140.49</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>608.6124087591242</t>
+          <t>607.7274052478134</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -6041,11 +6041,11 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>89.25</v>
+        <v>78</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>98.925</t>
+          <t>106.125</t>
         </is>
       </c>
       <c r="BL12" t="n">
@@ -6053,17 +6053,17 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-28</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-34.5032695580344</t>
+          <t>-34.75988864840453</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-38.8222887199465</t>
+          <t>-36.17129364544024</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -973,17 +973,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.79</v>
+        <v>0.89</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>19.93</v>
+        <v>19.99</v>
       </c>
       <c r="BA2" t="n">
         <v>20.29</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>118.73</t>
+          <t>188.06</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-121.04</t>
+          <t>-114.31</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,38 +1227,38 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>36.58</v>
+        <v>38.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>35.79166666666667</t>
+          <t>35.825</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>205.67</v>
+        <v>206.12</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-26.29232385512172</t>
+          <t>-24.90712403823361</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-20.12202059107051</t>
+          <t>-17.28852504534899</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>42.33333333333334</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1646,35 +1646,35 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.71</v>
+        <v>1.79</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="BA3" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>118.73</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-127.28</t>
+          <t>-121.04</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1718,15 +1718,15 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>40.78</v>
+        <v>36.58</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>41.59166666666667</t>
+          <t>35.79166666666667</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>207.31</v>
+        <v>205.67</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-27.41419717585831</t>
+          <t>-26.29232385512172</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-19.02265634956301</t>
+          <t>-20.12202059107051</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.04</v>
+        <v>0.19</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>19.89</v>
+        <v>19.92</v>
       </c>
       <c r="BA4" t="n">
-        <v>20.29</v>
+        <v>20.28</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>73.72</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-132.31</t>
+          <t>-127.28</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2201,38 +2201,38 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>40.98</v>
+        <v>40.78</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>49.29166666666667</t>
+          <t>41.59166666666667</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>208.03</v>
+        <v>207.31</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-28.93993187154836</t>
+          <t>-27.41419717585831</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-16.77275542063935</t>
+          <t>-19.02265634956301</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,174 +2409,174 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-16.86</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-44.42</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>2025-11-12 00:00:00</t>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2615,56 +2615,56 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.01</v>
+        <v>3.12</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>19.85</v>
+        <v>19.89</v>
       </c>
       <c r="BA5" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-135.07</t>
+          <t>-132.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2688,38 +2688,38 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>24.78</v>
+        <v>40.98</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>44.59166666666667</t>
+          <t>49.29166666666667</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>210.11</v>
+        <v>208.03</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-31.15214577171364</t>
+          <t>-28.93993187154836</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-26.2452985428684</t>
+          <t>-16.77275542063935</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>22.66666666666667</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -3107,35 +3107,35 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.21</v>
+        <v>-1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>19.86</v>
+        <v>19.85</v>
       </c>
       <c r="BA6" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -3144,15 +3144,15 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BD6" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BE6" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BE6" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BF6" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3179,34 +3179,34 @@
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>33.25</v>
+        <v>24.78</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>237.06</v>
+        <v>210.11</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3594,35 +3594,35 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="BA7" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BE7" t="n">
         <v>-0.12</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3662,38 +3662,38 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,42 +3870,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4076,40 +4076,40 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -4118,14 +4118,14 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4149,38 +4149,38 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4568,35 +4568,35 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="BA9" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="BE9" t="n">
         <v>-0.13</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4636,38 +4636,38 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5050,191 +5050,191 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>606.8449781659389</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>606.8449781659389</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BM10" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5537,40 +5537,40 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="BA11" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
@@ -5579,11 +5579,11 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BE11" t="n">
         <v>-0.14</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5610,38 +5610,38 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6024,40 +6024,40 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.6</v>
+        <v>-1.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20.04</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>20.43</v>
+        <v>20.42</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="BE12" t="n">
         <v>-0.14</v>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-138.55</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6097,38 +6097,38 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>89.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>102.125</t>
+          <t>74.225</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>338.94</v>
+        <v>315.32</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-34.7716465105192</t>
+          <t>-34.69999653321515</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-34.83631475214987</t>
+          <t>-34.30592165804288</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>365.38</t>
+          <t>365.8</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>19.99</v>
+        <v>20.04</v>
       </c>
       <c r="BA2" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>188.06</t>
+          <t>353.22</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-114.31</t>
+          <t>-107.60</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1231,29 +1231,29 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>38.4</v>
+        <v>42.33</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>35.825</t>
+          <t>33.55833333333334</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>206.12</v>
+        <v>205.28</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-24.90712403823361</t>
+          <t>-23.36339188423001</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-17.28852504534899</t>
+          <t>-14.8728650372102</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.79</v>
+        <v>0.89</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>19.93</v>
+        <v>19.99</v>
       </c>
       <c r="BA3" t="n">
         <v>20.29</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>118.73</t>
+          <t>188.06</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-121.04</t>
+          <t>-114.31</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1714,38 +1714,38 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>36.58</v>
+        <v>38.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>35.79166666666667</t>
+          <t>35.825</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>205.67</v>
+        <v>206.12</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-26.29232385512172</t>
+          <t>-24.90712403823361</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-20.12202059107051</t>
+          <t>-17.28852504534899</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>42.33333333333334</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -2118,7 +2118,7 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2133,35 +2133,35 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.71</v>
+        <v>1.79</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="BA4" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>118.73</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-127.28</t>
+          <t>-121.04</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2205,15 +2205,15 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>40.78</v>
+        <v>36.58</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>41.59166666666667</t>
+          <t>35.79166666666667</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>207.31</v>
+        <v>205.67</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-27.41419717585831</t>
+          <t>-26.29232385512172</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-19.02265634956301</t>
+          <t>-20.12202059107051</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,7 +2605,7 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.04</v>
+        <v>0.19</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>19.89</v>
+        <v>19.92</v>
       </c>
       <c r="BA5" t="n">
-        <v>20.29</v>
+        <v>20.28</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>73.72</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-132.31</t>
+          <t>-127.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2688,38 +2688,38 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>40.98</v>
+        <v>40.78</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>49.29166666666667</t>
+          <t>41.59166666666667</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>208.03</v>
+        <v>207.31</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-28.93993187154836</t>
+          <t>-27.41419717585831</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-16.77275542063935</t>
+          <t>-19.02265634956301</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,174 +2896,174 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-16.86</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-44.42</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>2025-11-12 00:00:00</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,7 +3092,7 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3102,56 +3102,56 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.01</v>
+        <v>3.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>19.85</v>
+        <v>19.89</v>
       </c>
       <c r="BA6" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-135.07</t>
+          <t>-132.31</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3175,38 +3175,38 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>24.78</v>
+        <v>40.98</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>44.59166666666667</t>
+          <t>49.29166666666667</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>210.11</v>
+        <v>208.03</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-31.15214577171364</t>
+          <t>-28.93993187154836</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-26.2452985428684</t>
+          <t>-16.77275542063935</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>22.66666666666667</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3579,7 +3579,7 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3594,35 +3594,35 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.21</v>
+        <v>-1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>19.86</v>
+        <v>19.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -3631,15 +3631,15 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BD7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="BE7" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BE7" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BF7" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>33.25</v>
+        <v>24.78</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>237.06</v>
+        <v>210.11</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,7 +4066,7 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4081,35 +4081,35 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.31</v>
+        <v>-1.21</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>19.9</v>
+        <v>19.86</v>
       </c>
       <c r="BA8" t="n">
-        <v>20.36</v>
+        <v>20.3</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BE8" t="n">
         <v>-0.12</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-134.12</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4149,38 +4149,38 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>35</v>
+        <v>33.25</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>42.525</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>271.17</v>
+        <v>237.06</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-32.04429981332186</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-27.87588519809319</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4357,42 +4357,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-43.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,7 +4553,7 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4563,40 +4563,40 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>76.19</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.9</v>
+        <v>-1.31</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.71</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4636,38 +4636,38 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>42.4</v>
+        <v>35</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>284.98</v>
+        <v>271.17</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-27</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-33.24920018540792</t>
+          <t>-32.80219337972708</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-31.5799835937355</t>
+          <t>-30.34365594848241</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.55</t>
+          <t>-29.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,7 +5040,7 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5055,35 +5055,35 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="BA10" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -5092,11 +5092,11 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="BE10" t="n">
         <v>-0.13</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-136.71</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5123,38 +5123,38 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>57.6</v>
+        <v>42.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>73.425</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>285.38</v>
+        <v>284.98</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-33.55269411116655</t>
+          <t>-33.24920018540792</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-30.0754522443208</t>
+          <t>-31.5799835937355</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-21.55</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,7 +5527,7 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5537,188 +5537,188 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19.91</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-136.71</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2025/12/17</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>606.8449781659389</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>73.425</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-33.55269411116655</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-30.0754522443208</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>時報</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-12.06591517969974</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>-15.35822892592142</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>6.139510302692406</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-138.27</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2025/12/17</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>606.8449781659389</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>71.025</t>
-        </is>
-      </c>
-      <c r="BM11" t="n">
-        <v>293.08</v>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-34.1849199051385</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-31.35199845071691</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>時報</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>-12.06591517969974</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>-15.35822892592142</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>6.139510302692406</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -5776,17 +5776,17 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,7 +6014,7 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -6024,40 +6024,40 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.25</v>
+        <v>-0.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="BA12" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -6066,11 +6066,11 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BE12" t="n">
         <v>-0.14</v>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-138.55</t>
+          <t>-138.27</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6097,38 +6097,38 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>51.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>74.225</t>
+          <t>71.025</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>315.32</v>
+        <v>293.08</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-34.69999653321515</t>
+          <t>-34.1849199051385</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-34.30592165804288</t>
+          <t>-31.35199845071691</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/出版產業.xlsx
+++ b/Result/checksun_type/出版產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW12"/>
+  <dimension ref="A1:CW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,174 +948,174 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>26.15</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-5.11</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>2025-11-12 00:00:00</t>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,67 +1144,67 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU2" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>2789.22</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>353.22</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-107.60</t>
+          <t>-99.79</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,24 +1222,24 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>42.33</v>
+        <v>56.93</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>33.55833333333334</t>
+          <t>48.85833333333333</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>205.28</v>
+        <v>204.2</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-23.36339188423001</t>
+          <t>-19.02390597899738</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-14.8728650372102</t>
+          <t>-1.463380828304039</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>42.33333333333334</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-13.53</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>19.99</v>
+        <v>20.07</v>
       </c>
       <c r="BA3" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>188.06</t>
+          <t>2063.39</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-114.31</t>
+          <t>-101.23</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1718,34 +1718,34 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>38.4</v>
+        <v>17.53</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>35.825</t>
+          <t>29.25833333333334</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>206.12</v>
+        <v>203.24</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-24.90712403823361</t>
+          <t>-22.2167287336689</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-17.28852504534899</t>
+          <t>-15.9100814055828</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>42.33333333333334</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,47 +2137,47 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>19.93</v>
+        <v>20.04</v>
       </c>
       <c r="BA4" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>118.73</t>
+          <t>353.22</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-121.04</t>
+          <t>-107.60</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>36.58</v>
+        <v>42.33</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>35.79166666666667</t>
+          <t>33.55833333333334</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>205.67</v>
+        <v>205.28</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-26.29232385512172</t>
+          <t>-23.36339188423001</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-20.12202059107051</t>
+          <t>-14.8728650372102</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>42.33333333333334</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2.71</v>
+        <v>0.89</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.19</v>
+        <v>1.65</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>19.92</v>
+        <v>19.99</v>
       </c>
       <c r="BA5" t="n">
-        <v>20.28</v>
+        <v>20.29</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>188.06</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-127.28</t>
+          <t>-114.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>40.78</v>
+        <v>38.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>41.59166666666667</t>
+          <t>35.825</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>207.31</v>
+        <v>206.12</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-27.41419717585831</t>
+          <t>-24.90712403823361</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-19.02265634956301</t>
+          <t>-17.28852504534899</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>42.33333333333334</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.86</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,52 +3107,52 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>3.12</v>
+        <v>1.79</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.04</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>19.89</v>
+        <v>19.93</v>
       </c>
       <c r="BA6" t="n">
         <v>20.29</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>118.73</t>
         </is>
       </c>
       <c r="BD6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE6" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BE6" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="BF6" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-132.31</t>
+          <t>-121.04</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>40.98</v>
+        <v>36.58</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>49.29166666666667</t>
+          <t>35.79166666666667</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>208.03</v>
+        <v>205.67</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-28.93993187154836</t>
+          <t>-26.29232385512172</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-16.77275542063935</t>
+          <t>-20.12202059107051</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,22 +3331,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3398,159 +3398,159 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-5.13</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-44.42</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>2025-11-12 00:00:00</t>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.01</v>
+        <v>2.71</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.26</v>
+        <v>0.19</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>19.85</v>
+        <v>19.92</v>
       </c>
       <c r="BA7" t="n">
         <v>20.28</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>73.72</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-135.07</t>
+          <t>-127.28</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>24.78</v>
+        <v>40.78</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>44.59166666666667</t>
+          <t>41.59166666666667</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>210.11</v>
+        <v>207.31</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-31.15214577171364</t>
+          <t>-27.41419717585831</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-26.2452985428684</t>
+          <t>-19.02265634956301</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>22.66666666666667</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,159 +3885,159 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-5.13</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-16.86</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>19.6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-21.81</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>19.85</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>2025-11-12 00:00:00</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -4085,44 +4085,44 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.21</v>
+        <v>3.12</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>19.86</v>
+        <v>19.89</v>
       </c>
       <c r="BA8" t="n">
-        <v>20.3</v>
+        <v>20.29</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="BE8" t="n">
         <v>-0.12</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-134.12</t>
+          <t>-132.31</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>33.25</v>
+        <v>40.98</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>42.525</t>
+          <t>49.29166666666667</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>237.06</v>
+        <v>208.03</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-32.04429981332186</t>
+          <t>-28.93993187154836</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-27.87588519809319</t>
+          <t>-16.77275542063935</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.73</t>
+          <t>-44.42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,35 +4568,35 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.31</v>
+        <v>-1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>19.9</v>
+        <v>19.85</v>
       </c>
       <c r="BA9" t="n">
-        <v>20.36</v>
+        <v>20.28</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-133.71</t>
+          <t>-135.07</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>606.8449781659389</t>
+          <t>606.3946220930233</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>35</v>
+        <v>24.78</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>44.59166666666667</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>271.17</v>
+        <v>210.11</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-27</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-32.80219337972708</t>
+          <t>-31.15214577171364</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-30.34365594848241</t>
+          <t>-26.2452985428684</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.66666666666667</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>365.8</t>
+          <t>364.91</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,22 +4792,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.57</t>
+          <t>-21.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t